--- a/NotasGeologiaPublicationList_Updated_1.xlsx
+++ b/NotasGeologiaPublicationList_Updated_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\mariantoc.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA996E2F-BE23-41CD-88A4-1C6D8A14F256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47B1FF42-3990-4D21-91BC-1941208159DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5245" uniqueCount="4777">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5257" uniqueCount="4793">
   <si>
     <t>Distribution of Mineral Occurrences in Northeastern South America</t>
   </si>
@@ -14704,6 +14704,54 @@
   </si>
   <si>
     <t>https://mariantoc.github.io/biography.html#FUNVISIS</t>
+  </si>
+  <si>
+    <t>Capítulo 7 del libro riesgo Sísmico en Caracas y Estrategias de una Mitigación. Universidad Central de Venezuela, Febrero 2024.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Si la naturaleza se opone……Terremotos, historia y sociedad en Venezuela. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rogelio Altéz </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Espectro de respuesta del terremoto de Caracas de 1967. Estimado a partir del daño. </t>
+  </si>
+  <si>
+    <t>Alfredo Urich y Oscar A. López</t>
+  </si>
+  <si>
+    <t>Editorial Alfa, Primera Edición, Venezuela, Octubre 2010.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gravimetría y tectónica de los márgenes meridional y oriental de la Placa del Caribe. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antonio E. Eshib </t>
+  </si>
+  <si>
+    <t>Primera Edición Digital, Ediciones de la Academia Nacional de la Ingeniería y el Hábitat, 2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estructura cortical de los Andes de Mérida, Venezuela. </t>
+  </si>
+  <si>
+    <t>Rondón, F.; Avila, J.; Schmitz, M.; Sánchez Rojas, J.; Medina, P.; Lolli, M.; Marchena, D.; Yegres, L.; Audemard, F.</t>
+  </si>
+  <si>
+    <t>Revista de la Facultad de Ingeniería, Universidad Central de Venezuela, Volumen 36, Número 2, 2021</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/biography.html#UrichALopezO2014</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/biography.html#AltezR2010</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/geophysics.html#EshibAE2021</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/structural.html#RondonFetal2021</t>
   </si>
 </sst>
 </file>
@@ -14799,7 +14847,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
@@ -14812,7 +14860,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -47019,13 +47066,13 @@
         <v>4716</v>
       </c>
       <c r="G1281" s="1" t="str">
-        <f t="shared" ref="G1281:G1301" si="41">HYPERLINK(F1281)</f>
+        <f t="shared" ref="G1281:G1305" si="41">HYPERLINK(F1281)</f>
         <v>https://mariantoc.github.io/minerals.html#Ayalaetal2010</v>
       </c>
     </row>
     <row r="1282" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1282">
-        <f t="shared" ref="A1282:A1301" si="42">A1281+1</f>
+        <f t="shared" ref="A1282:A1305" si="42">A1281+1</f>
         <v>1281</v>
       </c>
       <c r="B1282" t="s">
@@ -47481,7 +47528,7 @@
       <c r="E1300" t="s">
         <v>4771</v>
       </c>
-      <c r="F1300" s="8" t="s">
+      <c r="F1300" t="s">
         <v>4775</v>
       </c>
       <c r="G1300" s="1" t="str">
@@ -47500,7 +47547,7 @@
       <c r="E1301" t="s">
         <v>4774</v>
       </c>
-      <c r="F1301" s="8" t="s">
+      <c r="F1301" t="s">
         <v>4776</v>
       </c>
       <c r="G1301" s="1" t="str">
@@ -47509,23 +47556,103 @@
       </c>
     </row>
     <row r="1302" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1302" s="7" t="s">
-        <v>4315</v>
+      <c r="A1302">
+        <f t="shared" si="42"/>
+        <v>1301</v>
+      </c>
+      <c r="B1302" t="s">
+        <v>4780</v>
+      </c>
+      <c r="C1302" t="s">
+        <v>4781</v>
+      </c>
+      <c r="D1302">
+        <v>2014</v>
+      </c>
+      <c r="E1302" t="s">
+        <v>4777</v>
+      </c>
+      <c r="F1302" t="s">
+        <v>4789</v>
+      </c>
+      <c r="G1302" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/biography.html#UrichALopezO2014</v>
       </c>
     </row>
     <row r="1303" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1303" s="7" t="s">
-        <v>4315</v>
+      <c r="A1303">
+        <f t="shared" si="42"/>
+        <v>1302</v>
+      </c>
+      <c r="B1303" t="s">
+        <v>4778</v>
+      </c>
+      <c r="C1303" t="s">
+        <v>4779</v>
+      </c>
+      <c r="D1303">
+        <v>2010</v>
+      </c>
+      <c r="E1303" t="s">
+        <v>4782</v>
+      </c>
+      <c r="F1303" t="s">
+        <v>4790</v>
+      </c>
+      <c r="G1303" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/biography.html#AltezR2010</v>
       </c>
     </row>
     <row r="1304" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1304" s="7" t="s">
-        <v>4315</v>
+      <c r="A1304">
+        <f t="shared" si="42"/>
+        <v>1303</v>
+      </c>
+      <c r="B1304" t="s">
+        <v>4783</v>
+      </c>
+      <c r="C1304" t="s">
+        <v>4784</v>
+      </c>
+      <c r="D1304">
+        <v>2021</v>
+      </c>
+      <c r="E1304" t="s">
+        <v>4785</v>
+      </c>
+      <c r="F1304" t="s">
+        <v>4791</v>
+      </c>
+      <c r="G1304" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/geophysics.html#EshibAE2021</v>
       </c>
     </row>
     <row r="1305" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1305" s="7" t="s">
-        <v>4315</v>
+      <c r="A1305">
+        <f t="shared" si="42"/>
+        <v>1304</v>
+      </c>
+      <c r="B1305" t="s">
+        <v>4786</v>
+      </c>
+      <c r="C1305" t="s">
+        <v>4787</v>
+      </c>
+      <c r="D1305">
+        <v>2021</v>
+      </c>
+      <c r="E1305" t="s">
+        <v>4788</v>
+      </c>
+      <c r="F1305" t="s">
+        <v>4792</v>
+      </c>
+      <c r="G1305" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/structural.html#RondonFetal2021</v>
       </c>
     </row>
     <row r="1306" spans="1:7" x14ac:dyDescent="0.3">

--- a/NotasGeologiaPublicationList_Updated_1.xlsx
+++ b/NotasGeologiaPublicationList_Updated_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\mariantoc.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47B1FF42-3990-4D21-91BC-1941208159DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E3E6038-CE3E-4065-9F9C-781AA7896D91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -14682,9 +14682,6 @@
     <t>https://mariantoc.github.io/fields.html#PorrasJS2026</t>
   </si>
   <si>
-    <t xml:space="preserve">El Terremoto de Caracas de 1967: 50 año después. </t>
-  </si>
-  <si>
     <t xml:space="preserve">Carlos Genatios; Marianela Lafuente; Alfredo Cilento; José Grases (compiladores) </t>
   </si>
   <si>
@@ -14752,6 +14749,9 @@
   </si>
   <si>
     <t>https://mariantoc.github.io/structural.html#RondonFetal2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Terremoto de Caracas de 1967: 50 años después. </t>
   </si>
 </sst>
 </file>
@@ -47501,7 +47501,7 @@
         <v>2026</v>
       </c>
       <c r="E1299" t="s">
-        <v>4772</v>
+        <v>4771</v>
       </c>
       <c r="F1299" t="s">
         <v>4768</v>
@@ -47517,19 +47517,19 @@
         <v>1299</v>
       </c>
       <c r="B1300" t="s">
+        <v>4792</v>
+      </c>
+      <c r="C1300" t="s">
         <v>4769</v>
-      </c>
-      <c r="C1300" t="s">
-        <v>4770</v>
       </c>
       <c r="D1300">
         <v>2017</v>
       </c>
       <c r="E1300" t="s">
-        <v>4771</v>
+        <v>4770</v>
       </c>
       <c r="F1300" t="s">
-        <v>4775</v>
+        <v>4774</v>
       </c>
       <c r="G1300" s="1" t="str">
         <f t="shared" si="41"/>
@@ -47542,13 +47542,13 @@
         <v>1300</v>
       </c>
       <c r="B1301" t="s">
+        <v>4772</v>
+      </c>
+      <c r="E1301" t="s">
         <v>4773</v>
       </c>
-      <c r="E1301" t="s">
-        <v>4774</v>
-      </c>
       <c r="F1301" t="s">
-        <v>4776</v>
+        <v>4775</v>
       </c>
       <c r="G1301" s="1" t="str">
         <f t="shared" si="41"/>
@@ -47561,19 +47561,19 @@
         <v>1301</v>
       </c>
       <c r="B1302" t="s">
+        <v>4779</v>
+      </c>
+      <c r="C1302" t="s">
         <v>4780</v>
-      </c>
-      <c r="C1302" t="s">
-        <v>4781</v>
       </c>
       <c r="D1302">
         <v>2014</v>
       </c>
       <c r="E1302" t="s">
-        <v>4777</v>
+        <v>4776</v>
       </c>
       <c r="F1302" t="s">
-        <v>4789</v>
+        <v>4788</v>
       </c>
       <c r="G1302" s="1" t="str">
         <f t="shared" si="41"/>
@@ -47586,19 +47586,19 @@
         <v>1302</v>
       </c>
       <c r="B1303" t="s">
+        <v>4777</v>
+      </c>
+      <c r="C1303" t="s">
         <v>4778</v>
-      </c>
-      <c r="C1303" t="s">
-        <v>4779</v>
       </c>
       <c r="D1303">
         <v>2010</v>
       </c>
       <c r="E1303" t="s">
-        <v>4782</v>
+        <v>4781</v>
       </c>
       <c r="F1303" t="s">
-        <v>4790</v>
+        <v>4789</v>
       </c>
       <c r="G1303" s="1" t="str">
         <f t="shared" si="41"/>
@@ -47611,19 +47611,19 @@
         <v>1303</v>
       </c>
       <c r="B1304" t="s">
+        <v>4782</v>
+      </c>
+      <c r="C1304" t="s">
         <v>4783</v>
-      </c>
-      <c r="C1304" t="s">
-        <v>4784</v>
       </c>
       <c r="D1304">
         <v>2021</v>
       </c>
       <c r="E1304" t="s">
-        <v>4785</v>
+        <v>4784</v>
       </c>
       <c r="F1304" t="s">
-        <v>4791</v>
+        <v>4790</v>
       </c>
       <c r="G1304" s="1" t="str">
         <f t="shared" si="41"/>
@@ -47636,19 +47636,19 @@
         <v>1304</v>
       </c>
       <c r="B1305" t="s">
+        <v>4785</v>
+      </c>
+      <c r="C1305" t="s">
         <v>4786</v>
-      </c>
-      <c r="C1305" t="s">
-        <v>4787</v>
       </c>
       <c r="D1305">
         <v>2021</v>
       </c>
       <c r="E1305" t="s">
-        <v>4788</v>
+        <v>4787</v>
       </c>
       <c r="F1305" t="s">
-        <v>4792</v>
+        <v>4791</v>
       </c>
       <c r="G1305" s="1" t="str">
         <f t="shared" si="41"/>
